--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.62603165626539</v>
+        <v>9.851730144143126</v>
       </c>
       <c r="D2" t="n">
-        <v>62.23212839029821</v>
+        <v>10.11272086342346</v>
       </c>
       <c r="E2" t="n">
-        <v>12.58727770098542</v>
+        <v>2.04543262641013</v>
       </c>
       <c r="F2" t="n">
-        <v>12.46038517903643</v>
+        <v>2.02481259159342</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.02558811555025</v>
+        <v>9.916658068776917</v>
       </c>
       <c r="D3" t="n">
-        <v>60.52228312471642</v>
+        <v>9.834871007766418</v>
       </c>
       <c r="E3" t="n">
-        <v>12.58727770098542</v>
+        <v>2.04543262641013</v>
       </c>
       <c r="F3" t="n">
-        <v>12.46038517903643</v>
+        <v>2.02481259159342</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.86388830318547</v>
+        <v>5.01538184926764</v>
       </c>
       <c r="D4" t="n">
-        <v>31.73094411687835</v>
+        <v>5.156278418992732</v>
       </c>
       <c r="E4" t="n">
-        <v>12.58727770098542</v>
+        <v>2.04543262641013</v>
       </c>
       <c r="F4" t="n">
-        <v>12.46038517903643</v>
+        <v>2.02481259159342</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.68935052747232</v>
+        <v>9.374519460714252</v>
       </c>
       <c r="D5" t="n">
-        <v>58.19328980158063</v>
+        <v>9.456409592756852</v>
       </c>
       <c r="E5" t="n">
-        <v>12.58727770098542</v>
+        <v>2.04543262641013</v>
       </c>
       <c r="F5" t="n">
-        <v>12.46038517903643</v>
+        <v>2.02481259159342</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
